--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:11</t>
+    <t xml:space="preserve">2026-09-09 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:09</t>
+    <t xml:space="preserve">2026-09-17 13:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,34 +955,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>722189</v>
+        <v>812988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>725800</v>
+        <v>722189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>712500</v>
+        <v>725800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>812988</v>
+        <v>712500</v>
       </c>
     </row>
   </sheetData>
@@ -1015,134 +1015,134 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>577948</v>
+        <v>670420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>665767.5</v>
+        <v>768750</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>722189</v>
+        <v>812988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>595014</v>
+        <v>577948</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>671949</v>
+        <v>665767.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>725800</v>
+        <v>722189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>588011</v>
+        <v>595014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>668250</v>
+        <v>671949</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>712500</v>
+        <v>725800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>670420</v>
+        <v>588011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>768750</v>
+        <v>668250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>812988</v>
+        <v>712500</v>
       </c>
     </row>
     <row r="14">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:40</t>
+    <t xml:space="preserve">2026-09-25 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_maule.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:38</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
